--- a/data/1st Round/Results Table/CdS3_2_Results Table.xlsx
+++ b/data/1st Round/Results Table/CdS3_2_Results Table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fbdd27f2520478cf/Ambiente de Trabalho/TESE/Data_Analysis/data/CdS3_2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fbdd27f2520478cf/Ambiente de Trabalho/TESE/Data_Analysis/data/1st Round/Results Table/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{4ED32DB8-0106-4995-9EA8-7F7F7AA1EBA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1500" windowWidth="17280" windowHeight="8880" xr2:uid="{46E8946A-8411-4976-B7E1-9F974B214DBA}"/>
+    <workbookView xWindow="2232" yWindow="2232" windowWidth="17280" windowHeight="8880" xr2:uid="{46E8946A-8411-4976-B7E1-9F974B214DBA}"/>
   </bookViews>
   <sheets>
     <sheet name="2_CdS3_Results Table_1" sheetId="1" r:id="rId1"/>
